--- a/artfynd/A 21120-2024 artfynd.xlsx
+++ b/artfynd/A 21120-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127056447</v>
+        <v>127056448</v>
       </c>
       <c r="B2" t="n">
         <v>57743</v>
@@ -705,15 +705,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>födosökande</t>

--- a/artfynd/A 21120-2024 artfynd.xlsx
+++ b/artfynd/A 21120-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127056448</v>
       </c>
       <c r="B2" t="n">
-        <v>57743</v>
+        <v>57747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21120-2024 artfynd.xlsx
+++ b/artfynd/A 21120-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127056448</v>
       </c>
       <c r="B2" t="n">
-        <v>57747</v>
+        <v>57749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
